--- a/data/trans_bre/P7_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P7_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 10,05</t>
+          <t>0,18; 10,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 4,6</t>
+          <t>-5,32; 4,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 6,74</t>
+          <t>-2,59; 6,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 4,34</t>
+          <t>-4,09; 4,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 103,61</t>
+          <t>0,81; 115,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,75; 59,69</t>
+          <t>-41,46; 56,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 114,31</t>
+          <t>-26,3; 102,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 39,22</t>
+          <t>-26,11; 35,76</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 9,53</t>
+          <t>-0,36; 9,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 7,54</t>
+          <t>-2,07; 8,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 7,05</t>
+          <t>-2,91; 7,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 5,51</t>
+          <t>-2,23; 5,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 110,64</t>
+          <t>-3,67; 113,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 85,66</t>
+          <t>-17,26; 95,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 80,95</t>
+          <t>-21,36; 86,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 54,65</t>
+          <t>-14,66; 54,51</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 19,71</t>
+          <t>4,48; 19,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 9,12</t>
+          <t>-4,25; 9,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 19,32</t>
+          <t>2,62; 18,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 28,17</t>
+          <t>5,74; 28,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,11; 138,05</t>
+          <t>24,24; 132,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 46,12</t>
+          <t>-17,54; 45,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,12; 119,77</t>
+          <t>12,37; 117,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,61; 480,42</t>
+          <t>25,67; 522,22</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 8,99</t>
+          <t>1,56; 9,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 5,88</t>
+          <t>-2,59; 5,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 4,73</t>
+          <t>-2,72; 4,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,71; -0,17</t>
+          <t>-14,11; -0,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 50,77</t>
+          <t>7,5; 55,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 33,03</t>
+          <t>-12,19; 30,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 26,06</t>
+          <t>-13,17; 26,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,61; -0,76</t>
+          <t>-58,62; -0,48</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 16,5</t>
+          <t>3,87; 15,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,95; 22,9</t>
+          <t>13,26; 23,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,59; 14,03</t>
+          <t>4,72; 14,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 12,66</t>
+          <t>-1,11; 13,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,8; 86,55</t>
+          <t>14,27; 82,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,14; 143,15</t>
+          <t>61,96; 149,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,01; 71,14</t>
+          <t>19,51; 72,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 60,82</t>
+          <t>-3,49; 63,13</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,33; 35,24</t>
+          <t>28,5; 35,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>22,62; 31,34</t>
+          <t>22,78; 31,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,05; 29,44</t>
+          <t>22,26; 29,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,65; 30,84</t>
+          <t>23,38; 30,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>434,35; 1652,54</t>
+          <t>443,6; 1549,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>230,55; 1147,92</t>
+          <t>258,53; 1167,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>396,81; 1941,3</t>
+          <t>413,76; 1818,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>421,28; 2122,15</t>
+          <t>401,47; 1860,79</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,23; 15,25</t>
+          <t>11,13; 15,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,93; 11,72</t>
+          <t>8,01; 12,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,14; 10,12</t>
+          <t>6,21; 10,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,15; 9,85</t>
+          <t>2,14; 10,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>67,91; 104,04</t>
+          <t>67,01; 104,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,49; 75,0</t>
+          <t>44,6; 76,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,08; 68,02</t>
+          <t>36,6; 69,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,99; 72,93</t>
+          <t>13,5; 74,44</t>
         </is>
       </c>
     </row>
